--- a/AHK功能測試.xlsx
+++ b/AHK功能測試.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\大四上\dac\00專案\AHK_ChatGPT_無痕模式測試\ChatGPT_Excel_AHK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E7AE15-4D6F-4108-86A1-635EFF7F52B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CAECFA-EED8-44F6-A29E-E2D2E7B4ABF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3384" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="測試" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>問題</t>
   </si>
@@ -33,32 +33,148 @@
     <t>回答</t>
   </si>
   <si>
+    <t>網址1</t>
+  </si>
+  <si>
+    <t>網址2</t>
+  </si>
+  <si>
+    <t>網址3</t>
+  </si>
+  <si>
     <t>請只回答：紅、綠、藍。</t>
   </si>
   <si>
-    <t>請用一句話說明 Excel 的用途。</t>
-  </si>
-  <si>
-    <t>請將以下三個詞依字母順序排列：banana、apple、cherry。</t>
-  </si>
-  <si>
-    <t>紅、綠、藍</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excel 是一款試算表軟體，可用於整理資料、計算數據、分析資訊及製作圖表，幫助使用者提升工作效率。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>apple、banana、cherry</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>請用一句話說明 Excel 的用途，並提供 1 個 Microsoft 官方來源網址。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>請比較</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>屈臣氏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>康是美</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>的主要用途，列出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>點差異，並提供至少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>個官方來源網址。</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://page.line.me/vuh1969d</t>
+  </si>
+  <si>
+    <t>https://www.aswatson.com/zh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -81,9 +197,35 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -169,7 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -180,13 +322,26 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -402,47 +557,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1">
+    <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="54" customHeight="1">
+    <row r="2" spans="1:7" ht="13.8" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
-    <row r="3" spans="1:2" ht="54" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    <row r="3" spans="1:7" ht="26.4" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
     </row>
-    <row r="4" spans="1:2" ht="54" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="1:7" ht="26.4" customHeight="1">
+      <c r="A4" s="11" t="s">
         <v>7</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>